--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">

--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10">

--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">

--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1688</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10">

--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11">

--- a/aircraft/reports/top-aircraft-models-over-time.xlsx
+++ b/aircraft/reports/top-aircraft-models-over-time.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
